--- a/default_layout.xlsx
+++ b/default_layout.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="85">
   <si>
     <t xml:space="preserve">初聲</t>
   </si>
@@ -182,6 +182,99 @@
   </si>
   <si>
     <t xml:space="preserve">ㄾ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QWERTY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/</t>
   </si>
 </sst>
 </file>
@@ -191,11 +284,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Noto Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -214,21 +308,34 @@
     </font>
     <font>
       <sz val="16"/>
-      <name val="Adwaita Sans"/>
+      <name val="Source Han Sans CN"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Noto Serif"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Adwaita Sans"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2B2B2"/>
+        <bgColor rgb="FF969696"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -272,25 +379,37 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -302,6 +421,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFB2B2B2"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -416,331 +595,445 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="11.23046875" defaultRowHeight="14.35" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="0" width="5.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="5.52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="J3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="2" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-    </row>
-    <row r="7" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="2" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4"/>
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="4"/>
+      <c r="G8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2" t="s">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="2" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="3" t="s">
         <v>53</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E22" s="0"/>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A16:J16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/default_layout.xlsx
+++ b/default_layout.xlsx
@@ -55,33 +55,33 @@
     <t xml:space="preserve">ㅅ</t>
   </si>
   <si>
+    <t xml:space="preserve">ㅎ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㅇ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄴ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ㄹ</t>
   </si>
   <si>
-    <t xml:space="preserve">ㅇ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㄴ</t>
+    <t xml:space="preserve">ㅍ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㅊ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㅌ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㅋ</t>
   </si>
   <si>
     <t xml:space="preserve">ㅁ</t>
   </si>
   <si>
-    <t xml:space="preserve">ㅍ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㅊ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㅌ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㅋ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㅎ</t>
-  </si>
-  <si>
     <t xml:space="preserve">中聲</t>
   </si>
   <si>
@@ -151,37 +151,37 @@
     <t xml:space="preserve">終聲</t>
   </si>
   <si>
+    <t xml:space="preserve">ㄽ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄺ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄶ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄼ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ㄿ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ㄳ</t>
   </si>
   <si>
     <t xml:space="preserve">ㅀ</t>
   </si>
   <si>
-    <t xml:space="preserve">ㄶ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㄼ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㄿ</t>
-  </si>
-  <si>
     <t xml:space="preserve">ㅄ</t>
   </si>
   <si>
-    <t xml:space="preserve">ㄺ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㄽ</t>
-  </si>
-  <si>
     <t xml:space="preserve">ㄵ</t>
   </si>
   <si>
+    <t xml:space="preserve">ㄾ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ㄻ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㄾ</t>
   </si>
   <si>
     <t xml:space="preserve">QWERTY</t>
@@ -284,7 +284,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Noto Sans"/>
@@ -310,12 +310,18 @@
       <sz val="16"/>
       <name val="Source Han Sans CN"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="16"/>
       <name val="Noto Serif"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Source Han Sans CN"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -379,7 +385,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -400,6 +406,10 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -408,7 +418,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -595,7 +605,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultColWidth="11.23046875" defaultRowHeight="14.35" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="1" style="1" width="5.52"/>
@@ -653,7 +663,7 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -662,7 +672,7 @@
       <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="J3" s="4"/>
@@ -682,7 +692,7 @@
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="H4" s="4"/>
@@ -690,16 +700,16 @@
       <c r="J4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -794,16 +804,16 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="20.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
@@ -820,13 +830,13 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="7" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
@@ -835,16 +845,16 @@
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="5" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -867,8 +877,8 @@
       <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>48</v>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>12</v>
@@ -876,11 +886,11 @@
       <c r="H13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>11</v>
+      <c r="J13" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -896,137 +906,134 @@
       <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="5" t="s">
         <v>50</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J17" s="7" t="s">
+      <c r="J17" s="8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    <row r="18" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="20.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="7" t="s">
+      <c r="H19" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="0"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/default_layout.xlsx
+++ b/default_layout.xlsx
@@ -67,6 +67,9 @@
     <t xml:space="preserve">ㄹ</t>
   </si>
   <si>
+    <t xml:space="preserve">ㅁ</t>
+  </si>
+  <si>
     <t xml:space="preserve">ㅍ</t>
   </si>
   <si>
@@ -77,9 +80,6 @@
   </si>
   <si>
     <t xml:space="preserve">ㅋ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ㅁ</t>
   </si>
   <si>
     <t xml:space="preserve">中聲</t>
@@ -407,7 +407,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -663,7 +663,7 @@
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -672,29 +672,29 @@
       <c r="H3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="4"/>
+      <c r="J3" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="G4" s="3"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -845,16 +845,16 @@
       <c r="E12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="3" t="s">
         <v>46</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -877,7 +877,7 @@
       <c r="E13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -886,42 +886,42 @@
       <c r="H13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>19</v>
+      <c r="J13" s="3" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="3" t="s">
         <v>53</v>
       </c>
     </row>
